--- a/files/LIFE_Customer_Complaint_NLP_Tags.xlsx
+++ b/files/LIFE_Customer_Complaint_NLP_Tags.xlsx
@@ -26,26 +26,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,10 +59,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,22 +77,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,17 +489,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>LIFE Customer Complaint NLP Tags</t>
@@ -467,111 +510,886 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIFE_Customer_Complaint_NLP_Tags.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: LIFE_Customer_Complaint_NLP_Tags.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>FY2026 Plan</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Revenue (RM m)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2210</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CAGR ~9%</t>
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 01</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>265351.45</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (RM m)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>412</v>
-      </c>
-      <c r="C6" t="n">
-        <v>455</v>
-      </c>
-      <c r="D6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Margin lift</t>
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 02</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>184839.18</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 03</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7595.51</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 04</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>382954.24</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 05</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>176923.44</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 06</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>262206.94</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 07</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>286537.35</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 08</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>414394.62</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 09</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>54884.67</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 10</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>127049.12</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 11</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>156688.09</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 12</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>113770.43</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Above peer median</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Note: placeholder demo data — not real Zava figures.</t>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 13</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>235259.58</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 14</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>374593.12</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 15</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>32607.65</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 16</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>192867.57</v>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 17</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>224331.71</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 18</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>175182.62</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 19</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>220121.58</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 20</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>348774.75</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 21</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>41505.3</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 22</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>462091.35</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 23</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>465399.41</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 24</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>92413.82000000001</v>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 25</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>167264.84</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Materially complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 26</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>22934.39</v>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Renewal due Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 27</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>114723.81</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 28</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>228347.86</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 29</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>176360.17</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>LIFE Customer Complaint NLP Tags — line item 30</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>243898.84</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Tracking on plan</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
